--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Dreamland Gran Canaria.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Dreamland Gran Canaria.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>23.2707</v>
+        <v>31.3119</v>
       </c>
       <c r="E2" t="n">
-        <v>29.8918</v>
+        <v>39.1082</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.6209</v>
+        <v>-7.7961</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.1799</v>
+        <v>13.3645</v>
       </c>
       <c r="H2" t="n">
-        <v>5.423099999999999</v>
+        <v>12.4483</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.602500000000001</v>
+        <v>0.9158000000000008</v>
       </c>
       <c r="J2" t="n">
-        <v>24.9155</v>
+        <v>43.6483</v>
       </c>
       <c r="K2" t="n">
-        <v>16.1965</v>
+        <v>29.1207</v>
       </c>
       <c r="L2" t="n">
-        <v>8.718700000000002</v>
+        <v>14.5277</v>
       </c>
       <c r="M2" t="n">
-        <v>-26.0952</v>
+        <v>-30.2837</v>
       </c>
       <c r="N2" t="n">
-        <v>-10.7739</v>
+        <v>-16.6723</v>
       </c>
       <c r="O2" t="n">
-        <v>-15.3217</v>
+        <v>-13.6118</v>
       </c>
       <c r="P2" t="n">
-        <v>4.537000000000001</v>
+        <v>0.9109000000000007</v>
       </c>
       <c r="Q2" t="n">
-        <v>-39.0156</v>
+        <v>-52.5832</v>
       </c>
       <c r="R2" t="n">
-        <v>43.5519</v>
+        <v>53.4935</v>
       </c>
       <c r="S2" t="n">
-        <v>-14.5372</v>
+        <v>-23.8577</v>
       </c>
       <c r="T2" t="n">
-        <v>-9.871500000000001</v>
+        <v>-16.9117</v>
       </c>
       <c r="U2" t="n">
-        <v>-4.6658</v>
+        <v>-6.9462</v>
       </c>
       <c r="V2" t="n">
-        <v>34.4511</v>
+        <v>40.8952</v>
       </c>
       <c r="W2" t="n">
-        <v>53.8629</v>
+        <v>64.9546</v>
       </c>
       <c r="X2" t="n">
-        <v>-19.4118</v>
+        <v>-24.0595</v>
       </c>
     </row>
     <row r="3">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>8.533899999999999</v>
+        <v>19.3293</v>
       </c>
       <c r="E3" t="n">
-        <v>23.2909</v>
+        <v>29.1861</v>
       </c>
       <c r="F3" t="n">
-        <v>-14.7567</v>
+        <v>-9.8568</v>
       </c>
       <c r="G3" t="n">
-        <v>9.321200000000001</v>
+        <v>11.3517</v>
       </c>
       <c r="H3" t="n">
-        <v>14.7185</v>
+        <v>14.9215</v>
       </c>
       <c r="I3" t="n">
-        <v>-5.3972</v>
+        <v>-3.5696</v>
       </c>
       <c r="J3" t="n">
-        <v>38.9331</v>
+        <v>43.4599</v>
       </c>
       <c r="K3" t="n">
-        <v>21.9161</v>
+        <v>26.6935</v>
       </c>
       <c r="L3" t="n">
-        <v>17.0176</v>
+        <v>16.7661</v>
       </c>
       <c r="M3" t="n">
-        <v>-29.6121</v>
+        <v>-32.108</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.1973</v>
+        <v>-11.7718</v>
       </c>
       <c r="O3" t="n">
-        <v>-22.4149</v>
+        <v>-20.3362</v>
       </c>
       <c r="P3" t="n">
-        <v>14.2904</v>
+        <v>17.7552</v>
       </c>
       <c r="Q3" t="n">
-        <v>-30.169</v>
+        <v>-34.6002</v>
       </c>
       <c r="R3" t="n">
-        <v>44.4595</v>
+        <v>52.3557</v>
       </c>
       <c r="S3" t="n">
-        <v>12.3873</v>
+        <v>18.6814</v>
       </c>
       <c r="T3" t="n">
-        <v>5.0453</v>
+        <v>7.080299999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>7.3422</v>
+        <v>11.6017</v>
       </c>
       <c r="V3" t="n">
-        <v>-27.4649</v>
+        <v>-28.4594</v>
       </c>
       <c r="W3" t="n">
-        <v>9.4808</v>
+        <v>13.2465</v>
       </c>
       <c r="X3" t="n">
-        <v>-36.9458</v>
+        <v>-41.7057</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>6.033200000000001</v>
+        <v>6.2363</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3081</v>
+        <v>1.0188</v>
       </c>
       <c r="F4" t="n">
-        <v>4.7251</v>
+        <v>5.2175</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2407999999999997</v>
+        <v>0.3866999999999998</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4430999999999998</v>
+        <v>0.5347999999999997</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2019000000000001</v>
+        <v>-0.148</v>
       </c>
       <c r="J4" t="n">
-        <v>13.2774</v>
+        <v>13.0471</v>
       </c>
       <c r="K4" t="n">
-        <v>7.059200000000001</v>
+        <v>6.937</v>
       </c>
       <c r="L4" t="n">
-        <v>6.218</v>
+        <v>6.110300000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-13.0365</v>
+        <v>-12.66</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.6165</v>
+        <v>-6.4021</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.4198</v>
+        <v>-6.2583</v>
       </c>
       <c r="P4" t="n">
-        <v>17.0123</v>
+        <v>17.0723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-10.888</v>
+        <v>-10.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>27.9006</v>
+        <v>27.9988</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.2862</v>
+        <v>-2.293</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.9454</v>
+        <v>-2.9237</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6593</v>
+        <v>0.6305999999999998</v>
       </c>
       <c r="V4" t="n">
-        <v>-8.933999999999999</v>
+        <v>-8.930099999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8645</v>
+        <v>1.822</v>
       </c>
       <c r="X4" t="n">
-        <v>-10.7983</v>
+        <v>-10.7517</v>
       </c>
     </row>
     <row r="5">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>3.531299999999999</v>
+        <v>4.672199999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>8.905200000000001</v>
+        <v>9.504899999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.3735</v>
+        <v>-4.8325</v>
       </c>
       <c r="G5" t="n">
-        <v>2.888100000000001</v>
+        <v>3.849399999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>6.0591</v>
+        <v>6.693499999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.1709</v>
+        <v>-2.8441</v>
       </c>
       <c r="J5" t="n">
-        <v>21.2227</v>
+        <v>22.0411</v>
       </c>
       <c r="K5" t="n">
-        <v>14.6947</v>
+        <v>14.9367</v>
       </c>
       <c r="L5" t="n">
-        <v>6.527699999999999</v>
+        <v>7.1044</v>
       </c>
       <c r="M5" t="n">
-        <v>-18.3344</v>
+        <v>-18.1914</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.636099999999999</v>
+        <v>-8.2431</v>
       </c>
       <c r="O5" t="n">
-        <v>-9.698399999999999</v>
+        <v>-9.948500000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>4.5368</v>
+        <v>4.7804</v>
       </c>
       <c r="Q5" t="n">
-        <v>-25.4053</v>
+        <v>-25.4947</v>
       </c>
       <c r="R5" t="n">
-        <v>29.9419</v>
+        <v>30.275</v>
       </c>
       <c r="S5" t="n">
-        <v>15.2215</v>
+        <v>14.918</v>
       </c>
       <c r="T5" t="n">
-        <v>11.7052</v>
+        <v>11.6516</v>
       </c>
       <c r="U5" t="n">
-        <v>3.5169</v>
+        <v>3.2661</v>
       </c>
       <c r="V5" t="n">
-        <v>-19.1148</v>
+        <v>-18.8752</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3828</v>
+        <v>1.3071</v>
       </c>
       <c r="X5" t="n">
-        <v>-20.4977</v>
+        <v>-20.1821</v>
       </c>
     </row>
     <row r="6">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9379</v>
+        <v>3.3056</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6907999999999999</v>
+        <v>1.7618</v>
       </c>
       <c r="F6" t="n">
-        <v>1.247</v>
+        <v>1.5435</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2169</v>
+        <v>-2.1853</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3351</v>
+        <v>-0.4776</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8816</v>
+        <v>-1.708</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8600000000000001</v>
+        <v>-0.8724999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1634</v>
+        <v>1.1613</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.0231</v>
+        <v>-2.0338</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3569</v>
+        <v>-1.3128</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4985</v>
+        <v>-1.6391</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1416000000000002</v>
+        <v>0.3257</v>
       </c>
       <c r="P6" t="n">
-        <v>4.5366</v>
+        <v>4.7802</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>5.8976</v>
+        <v>6.146</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3017</v>
+        <v>1.3095</v>
       </c>
       <c r="T6" t="n">
-        <v>2.108</v>
+        <v>2.1218</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8063</v>
+        <v>-0.8123</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6838</v>
+        <v>-0.5988</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8036000000000001</v>
+        <v>1.8785</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4874</v>
+        <v>-2.4771</v>
       </c>
     </row>
     <row r="7">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7865</v>
+        <v>1.6166</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9013</v>
+        <v>2.3453</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8852</v>
+        <v>-0.7286999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6146</v>
+        <v>1.3018</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0145</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6291</v>
+        <v>0.3711</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0173</v>
+        <v>1.4594</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0173</v>
+        <v>1.3476</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1117</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5973000000000001</v>
+        <v>-0.1576</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0318</v>
+        <v>-0.417</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6291</v>
+        <v>0.2593</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3744</v>
+        <v>-0.23</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2087</v>
+        <v>0.232</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1657</v>
+        <v>-0.462</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.792</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. METU</t>
+          <t>M. SALVO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.6663</v>
+        <v>-4.0992</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.325</v>
+        <v>-0.5499999999999998</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6587999999999996</v>
+        <v>-3.549100000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.194</v>
+        <v>-6.093800000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.1987</v>
+        <v>0.1699000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0048</v>
+        <v>-6.263599999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>5.673400000000001</v>
+        <v>6.803099999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7483000000000001</v>
+        <v>2.1734</v>
       </c>
       <c r="L8" t="n">
-        <v>4.9253</v>
+        <v>4.6295</v>
       </c>
       <c r="M8" t="n">
-        <v>-7.8674</v>
+        <v>-12.8966</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.9469</v>
+        <v>-2.0036</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.9205</v>
+        <v>-10.8931</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.4854</v>
+        <v>3.186799999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-17.4661</v>
+        <v>-12.7473</v>
       </c>
       <c r="R8" t="n">
-        <v>9.980599999999999</v>
+        <v>15.9341</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9804999999999999</v>
+        <v>2.3023</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.238</v>
+        <v>-0.4548</v>
       </c>
       <c r="U8" t="n">
-        <v>3.2185</v>
+        <v>2.7568</v>
       </c>
       <c r="V8" t="n">
-        <v>5.0329</v>
+        <v>-3.4948</v>
       </c>
       <c r="W8" t="n">
-        <v>9.7057</v>
+        <v>5.8491</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.672800000000001</v>
+        <v>-9.343999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SALVO</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.094</v>
+        <v>-4.950599999999998</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2208000000000001</v>
+        <v>15.8195</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.8733</v>
+        <v>-20.7702</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.069199999999999</v>
+        <v>-16.1531</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2317999999999995</v>
+        <v>3.3528</v>
       </c>
       <c r="I9" t="n">
-        <v>-6.301</v>
+        <v>-19.5056</v>
       </c>
       <c r="J9" t="n">
-        <v>7.074999999999999</v>
+        <v>18.4901</v>
       </c>
       <c r="K9" t="n">
-        <v>2.371</v>
+        <v>21.4416</v>
       </c>
       <c r="L9" t="n">
-        <v>4.704</v>
+        <v>-2.9517</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.1443</v>
+        <v>-34.6434</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.1391</v>
+        <v>-18.0887</v>
       </c>
       <c r="O9" t="n">
-        <v>-11.0051</v>
+        <v>-16.5543</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1756</v>
+        <v>13.4304</v>
       </c>
       <c r="Q9" t="n">
-        <v>-12.7026</v>
+        <v>-34.8279</v>
       </c>
       <c r="R9" t="n">
-        <v>15.8781</v>
+        <v>48.2582</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2957</v>
+        <v>25.9409</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4746</v>
+        <v>17.634</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7706</v>
+        <v>8.307599999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.496599999999999</v>
+        <v>-28.1685</v>
       </c>
       <c r="W9" t="n">
-        <v>5.8812</v>
+        <v>14.5233</v>
       </c>
       <c r="X9" t="n">
-        <v>-9.377800000000001</v>
+        <v>-42.6917</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.972399999999999</v>
+        <v>-4.9811</v>
       </c>
       <c r="E10" t="n">
-        <v>13.5087</v>
+        <v>-7.9912</v>
       </c>
       <c r="F10" t="n">
-        <v>-18.481</v>
+        <v>3.0099</v>
       </c>
       <c r="G10" t="n">
-        <v>-12.8608</v>
+        <v>-17.3955</v>
       </c>
       <c r="H10" t="n">
-        <v>5.131100000000001</v>
+        <v>-13.2882</v>
       </c>
       <c r="I10" t="n">
-        <v>-17.9916</v>
+        <v>-4.107200000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>15.2392</v>
+        <v>-5.980900000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>18.1809</v>
+        <v>-3.4128</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.9418</v>
+        <v>-2.5684</v>
       </c>
       <c r="M10" t="n">
-        <v>-28.1001</v>
+        <v>-11.4147</v>
       </c>
       <c r="N10" t="n">
-        <v>-13.0497</v>
+        <v>-9.8759</v>
       </c>
       <c r="O10" t="n">
-        <v>-15.0499</v>
+        <v>-1.5388</v>
       </c>
       <c r="P10" t="n">
-        <v>10.6611</v>
+        <v>13.2025</v>
       </c>
       <c r="Q10" t="n">
-        <v>-29.9421</v>
+        <v>-6.6014</v>
       </c>
       <c r="R10" t="n">
-        <v>40.6033</v>
+        <v>19.8039</v>
       </c>
       <c r="S10" t="n">
-        <v>21.2658</v>
+        <v>-0.9087000000000003</v>
       </c>
       <c r="T10" t="n">
-        <v>16.7377</v>
+        <v>0.2184000000000002</v>
       </c>
       <c r="U10" t="n">
-        <v>4.5279</v>
+        <v>-1.127</v>
       </c>
       <c r="V10" t="n">
-        <v>-24.0387</v>
+        <v>0.1202999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>11.4738</v>
+        <v>4.3729</v>
       </c>
       <c r="X10" t="n">
-        <v>-35.5122</v>
+        <v>-4.2526</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>B. JEFFERSON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6319</v>
+        <v>-10.2139</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.232099999999999</v>
+        <v>-6.6593</v>
       </c>
       <c r="F11" t="n">
-        <v>1.600200000000001</v>
+        <v>-3.5545</v>
       </c>
       <c r="G11" t="n">
-        <v>-17.5478</v>
+        <v>-2.2592</v>
       </c>
       <c r="H11" t="n">
-        <v>-9.883700000000001</v>
+        <v>-5.0317</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.6637</v>
+        <v>2.7727</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.025</v>
+        <v>1.1257</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.7648</v>
+        <v>-1.3661</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.2602</v>
+        <v>2.4915</v>
       </c>
       <c r="M11" t="n">
-        <v>-10.5225</v>
+        <v>-3.3847</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.1189</v>
+        <v>-3.6657</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.4034</v>
+        <v>0.281</v>
       </c>
       <c r="P11" t="n">
-        <v>11.3415</v>
+        <v>0.2277000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.444</v>
+        <v>-4.7803</v>
       </c>
       <c r="R11" t="n">
-        <v>16.7855</v>
+        <v>5.008</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7949</v>
+        <v>-5.3009</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1662</v>
+        <v>-4.2518</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6287</v>
+        <v>-1.0491</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3689</v>
+        <v>-2.8814</v>
       </c>
       <c r="W11" t="n">
-        <v>4.403</v>
+        <v>1.2473</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.0342</v>
+        <v>-4.1287</v>
       </c>
     </row>
     <row r="12">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.7359</v>
+        <v>-10.6647</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.8548</v>
+        <v>-11.6181</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1189999999999999</v>
+        <v>0.9536</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4372</v>
+        <v>-2.496099999999998</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.480400000000001</v>
+        <v>-4.1967</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9568000000000003</v>
+        <v>1.700199999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>7.085400000000001</v>
+        <v>6.9053</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9979</v>
+        <v>1.0451</v>
       </c>
       <c r="L12" t="n">
-        <v>4.0874</v>
+        <v>5.8602</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.523</v>
+        <v>-9.4017</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.4783</v>
+        <v>-5.241400000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.0444</v>
+        <v>-4.1601</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.3097</v>
+        <v>-5.4631</v>
       </c>
       <c r="Q12" t="n">
-        <v>-30.6227</v>
+        <v>-34.1452</v>
       </c>
       <c r="R12" t="n">
-        <v>26.3126</v>
+        <v>28.6817</v>
       </c>
       <c r="S12" t="n">
-        <v>2.051699999999999</v>
+        <v>1.7331</v>
       </c>
       <c r="T12" t="n">
-        <v>6.748</v>
+        <v>6.7328</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.6963</v>
+        <v>-4.9996</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.0401</v>
+        <v>-4.4383</v>
       </c>
       <c r="W12" t="n">
-        <v>8.9344</v>
+        <v>8.888399999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.9745</v>
+        <v>-13.3267</v>
       </c>
     </row>
     <row r="13">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.0313</v>
+        <v>-16.2193</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.9871</v>
+        <v>-19.5786</v>
       </c>
       <c r="F13" t="n">
-        <v>1.956</v>
+        <v>3.3598</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.926</v>
+        <v>-0.1107000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5512</v>
+        <v>-1.039400000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.3746</v>
+        <v>0.9280999999999998</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7094</v>
+        <v>10.1832</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7546</v>
+        <v>6.351100000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.0453</v>
+        <v>3.832</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.6348</v>
+        <v>-10.2942</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.3058</v>
+        <v>-7.3902</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.3293</v>
+        <v>-2.904</v>
       </c>
       <c r="P13" t="n">
-        <v>-10.8881</v>
+        <v>-17.3002</v>
       </c>
       <c r="Q13" t="n">
-        <v>-20.6417</v>
+        <v>-31.1857</v>
       </c>
       <c r="R13" t="n">
-        <v>9.7539</v>
+        <v>13.8857</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3782</v>
+        <v>-4.0263</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.5898</v>
+        <v>-6.762</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2117</v>
+        <v>2.7358</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1608000000000001</v>
+        <v>5.2182</v>
       </c>
       <c r="W13" t="n">
-        <v>3.5353</v>
+        <v>8.1861</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.3746</v>
+        <v>-2.9678</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. ANGOLA</t>
+          <t>C. METU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.5685</v>
+        <v>-17.8845</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.8331</v>
+        <v>-15.5345</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.7354</v>
+        <v>-2.3501</v>
       </c>
       <c r="G14" t="n">
-        <v>-11.9258</v>
+        <v>-7.9374</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.382099999999999</v>
+        <v>-9.126900000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.543400000000001</v>
+        <v>1.1894</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8666999999999998</v>
+        <v>8.6617</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.3966</v>
+        <v>2.1748</v>
       </c>
       <c r="L14" t="n">
-        <v>3.53</v>
+        <v>6.486800000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.0588</v>
+        <v>-16.5991</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.9855</v>
+        <v>-11.3015</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.0734</v>
+        <v>-5.2976</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.2172</v>
+        <v>-15.0237</v>
       </c>
       <c r="Q14" t="n">
-        <v>-26.7664</v>
+        <v>-33.4617</v>
       </c>
       <c r="R14" t="n">
-        <v>21.5493</v>
+        <v>18.4381</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.8397</v>
+        <v>-3.2694</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2841000000000001</v>
+        <v>-6.8622</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.5556</v>
+        <v>3.5926</v>
       </c>
       <c r="V14" t="n">
-        <v>1.414200000000001</v>
+        <v>8.3461</v>
       </c>
       <c r="W14" t="n">
-        <v>12.0842</v>
+        <v>16.1276</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.6701</v>
+        <v>-7.7816</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. ROBERTSON</t>
+          <t>B. ANGOLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>-30.5228</v>
+        <v>-19.7123</v>
       </c>
       <c r="E15" t="n">
-        <v>-27.5448</v>
+        <v>-16.391</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.9777</v>
+        <v>-3.321200000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-18.2337</v>
+        <v>-12.0341</v>
       </c>
       <c r="H15" t="n">
-        <v>-16.7858</v>
+        <v>-8.3781</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4477</v>
+        <v>-3.656100000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.2401</v>
+        <v>-1.2879</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.938499999999999</v>
+        <v>-4.577</v>
       </c>
       <c r="L15" t="n">
-        <v>2.698799999999999</v>
+        <v>3.288900000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-14.9936</v>
+        <v>-10.746</v>
       </c>
       <c r="N15" t="n">
-        <v>-10.8471</v>
+        <v>-3.8012</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.1466</v>
+        <v>-6.944599999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.4026</v>
+        <v>-5.2355</v>
       </c>
       <c r="Q15" t="n">
-        <v>-24.498</v>
+        <v>-26.8608</v>
       </c>
       <c r="R15" t="n">
-        <v>21.0956</v>
+        <v>21.6252</v>
       </c>
       <c r="S15" t="n">
-        <v>-12.1908</v>
+        <v>-3.8477</v>
       </c>
       <c r="T15" t="n">
-        <v>-10.3162</v>
+        <v>-0.2564999999999998</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.8743</v>
+        <v>-3.5913</v>
       </c>
       <c r="V15" t="n">
-        <v>3.3039</v>
+        <v>1.405</v>
       </c>
       <c r="W15" t="n">
-        <v>10.5093</v>
+        <v>12.014</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.2055</v>
+        <v>-10.609</v>
       </c>
     </row>
     <row r="16">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>-31.4618</v>
+        <v>-37.524</v>
       </c>
       <c r="E16" t="n">
-        <v>-18.3919</v>
+        <v>-25.7014</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.0703</v>
+        <v>-11.8223</v>
       </c>
       <c r="G16" t="n">
-        <v>-10.5355</v>
+        <v>-14.7218</v>
       </c>
       <c r="H16" t="n">
-        <v>2.011999999999999</v>
+        <v>-0.9595999999999993</v>
       </c>
       <c r="I16" t="n">
-        <v>-12.5475</v>
+        <v>-13.7623</v>
       </c>
       <c r="J16" t="n">
-        <v>29.6649</v>
+        <v>35.6272</v>
       </c>
       <c r="K16" t="n">
-        <v>21.7332</v>
+        <v>27.4363</v>
       </c>
       <c r="L16" t="n">
-        <v>7.9318</v>
+        <v>8.190999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-40.2004</v>
+        <v>-50.3492</v>
       </c>
       <c r="N16" t="n">
-        <v>-19.7213</v>
+        <v>-28.396</v>
       </c>
       <c r="O16" t="n">
-        <v>-20.4792</v>
+        <v>-21.9533</v>
       </c>
       <c r="P16" t="n">
-        <v>2.949</v>
+        <v>0.9105999999999987</v>
       </c>
       <c r="Q16" t="n">
-        <v>-59.2034</v>
+        <v>-71.93170000000001</v>
       </c>
       <c r="R16" t="n">
-        <v>62.1525</v>
+        <v>72.8421</v>
       </c>
       <c r="S16" t="n">
-        <v>-19.3178</v>
+        <v>-23.7487</v>
       </c>
       <c r="T16" t="n">
-        <v>-18.9021</v>
+        <v>-23.6739</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4157999999999996</v>
+        <v>-0.07499999999999984</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.5572</v>
+        <v>0.0363</v>
       </c>
       <c r="W16" t="n">
-        <v>30.049</v>
+        <v>34.2768</v>
       </c>
       <c r="X16" t="n">
-        <v>-34.606</v>
+        <v>-34.2402</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>K. ROBERTSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,148 +1732,226 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>-65.82810000000001</v>
+        <v>-46.4258</v>
       </c>
       <c r="E17" t="n">
-        <v>-51.9275</v>
+        <v>-38.866</v>
       </c>
       <c r="F17" t="n">
-        <v>-13.9006</v>
+        <v>-7.5597</v>
       </c>
       <c r="G17" t="n">
-        <v>-32.4689</v>
+        <v>-24.9571</v>
       </c>
       <c r="H17" t="n">
-        <v>-11.728</v>
+        <v>-28.1766</v>
       </c>
       <c r="I17" t="n">
-        <v>-20.7408</v>
+        <v>3.219600000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>8.0143</v>
+        <v>-5.1966</v>
       </c>
       <c r="K17" t="n">
-        <v>4.949199999999999</v>
+        <v>-13.9295</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0655</v>
+        <v>8.732999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-40.4832</v>
+        <v>-19.7606</v>
       </c>
       <c r="N17" t="n">
-        <v>-16.6772</v>
+        <v>-14.2471</v>
       </c>
       <c r="O17" t="n">
-        <v>-23.8059</v>
+        <v>-5.5133</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.495200000000001</v>
+        <v>-6.146300000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-52.6252</v>
+        <v>-32.779</v>
       </c>
       <c r="R17" t="n">
-        <v>50.1302</v>
+        <v>26.6331</v>
       </c>
       <c r="S17" t="n">
-        <v>-28.2292</v>
+        <v>-20.3801</v>
       </c>
       <c r="T17" t="n">
-        <v>-17.0546</v>
+        <v>-15.1544</v>
       </c>
       <c r="U17" t="n">
-        <v>-11.1748</v>
+        <v>-5.2253</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.6352</v>
+        <v>5.0574</v>
       </c>
       <c r="W17" t="n">
-        <v>9.738099999999999</v>
+        <v>14.2644</v>
       </c>
       <c r="X17" t="n">
-        <v>-12.3732</v>
+        <v>-9.207099999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>A. ALBICY</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dreamland Gran Canaria</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>32</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-75.5706</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-59.7932</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-15.777</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-35.8247</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-14.4115</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-21.4132</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10.0047</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.9975</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.0074</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-45.8299</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-21.4091</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-24.4204</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-4.3251</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-60.3224</v>
+      </c>
+      <c r="R18" t="n">
+        <v>55.9974</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-32.775</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-20.2425</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-12.5325</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-2.645299999999999</v>
+      </c>
+      <c r="W18" t="n">
+        <v>10.767</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-13.4125</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Dreamland Gran Canaria</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>28</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-146.4195</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-74.8203</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-71.59809999999999</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-109.531</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-19.34080000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-90.18730000000001</v>
-      </c>
-      <c r="J18" t="n">
-        <v>160.8358</v>
-      </c>
-      <c r="K18" t="n">
-        <v>102.6824</v>
-      </c>
-      <c r="L18" t="n">
-        <v>58.1544</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-270.3659</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-122.0239</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-148.3418</v>
-      </c>
-      <c r="P18" t="n">
-        <v>39.69580000000001</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-386.7511</v>
-      </c>
-      <c r="R18" t="n">
-        <v>426.4468000000001</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-28.4442</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-23.707</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-4.736199999999999</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-48.1408</v>
-      </c>
-      <c r="W18" t="n">
-        <v>174.8013</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-222.9419</v>
+      <c r="C19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-181.7741</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-103.9387</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-77.8339</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-111.9147</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-46.0346</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-65.88079999999999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>208.1189</v>
+      </c>
+      <c r="K19" t="n">
+        <v>124.5312</v>
+      </c>
+      <c r="L19" t="n">
+        <v>83.58659999999999</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-320.0336</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-170.5658</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-149.4683</v>
+      </c>
+      <c r="P19" t="n">
+        <v>22.76309999999999</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-475.7519</v>
+      </c>
+      <c r="R19" t="n">
+        <v>498.5146999999999</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-55.7523</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-51.82259999999999</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-3.929100000000004</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-36.8686</v>
+      </c>
+      <c r="W19" t="n">
+        <v>215.5176</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-252.3852</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Dreamland Gran Canaria.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Dreamland Gran Canaria.xlsx
@@ -565,13 +565,13 @@
         <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>31.3119</v>
+        <v>46.28919999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>39.1082</v>
+        <v>46.29199999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.7961</v>
+        <v>-0.002899999999999459</v>
       </c>
       <c r="G2" t="n">
         <v>13.3645</v>
@@ -610,13 +610,13 @@
         <v>53.4935</v>
       </c>
       <c r="S2" t="n">
-        <v>-23.8577</v>
+        <v>-8.8813</v>
       </c>
       <c r="T2" t="n">
-        <v>-16.9117</v>
+        <v>-9.728400000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-6.9462</v>
+        <v>0.8469999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>40.8952</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>L. LABEYRIE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>19.3293</v>
+        <v>5.94</v>
       </c>
       <c r="E3" t="n">
-        <v>29.1861</v>
+        <v>0.2735000000000012</v>
       </c>
       <c r="F3" t="n">
-        <v>-9.8568</v>
+        <v>5.666599999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>11.3517</v>
+        <v>0.3866999999999998</v>
       </c>
       <c r="H3" t="n">
-        <v>14.9215</v>
+        <v>0.5347999999999997</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.5696</v>
+        <v>-0.148</v>
       </c>
       <c r="J3" t="n">
-        <v>43.4599</v>
+        <v>13.0471</v>
       </c>
       <c r="K3" t="n">
-        <v>26.6935</v>
+        <v>6.937</v>
       </c>
       <c r="L3" t="n">
-        <v>16.7661</v>
+        <v>6.110300000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-32.108</v>
+        <v>-12.66</v>
       </c>
       <c r="N3" t="n">
-        <v>-11.7718</v>
+        <v>-6.4021</v>
       </c>
       <c r="O3" t="n">
-        <v>-20.3362</v>
+        <v>-6.2583</v>
       </c>
       <c r="P3" t="n">
-        <v>17.7552</v>
+        <v>17.0723</v>
       </c>
       <c r="Q3" t="n">
-        <v>-34.6002</v>
+        <v>-10.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>52.3557</v>
+        <v>27.9988</v>
       </c>
       <c r="S3" t="n">
-        <v>18.6814</v>
+        <v>-2.5889</v>
       </c>
       <c r="T3" t="n">
-        <v>7.080299999999999</v>
+        <v>-3.6691</v>
       </c>
       <c r="U3" t="n">
-        <v>11.6017</v>
+        <v>1.0797</v>
       </c>
       <c r="V3" t="n">
-        <v>-28.4594</v>
+        <v>-8.930099999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>13.2465</v>
+        <v>1.822</v>
       </c>
       <c r="X3" t="n">
-        <v>-41.7057</v>
+        <v>-10.7517</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. LABEYRIE</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>6.2363</v>
+        <v>5.553999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0188</v>
+        <v>22.1771</v>
       </c>
       <c r="F4" t="n">
-        <v>5.2175</v>
+        <v>-16.6229</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3866999999999998</v>
+        <v>11.3517</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5347999999999997</v>
+        <v>14.9215</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.148</v>
+        <v>-3.5696</v>
       </c>
       <c r="J4" t="n">
-        <v>13.0471</v>
+        <v>43.4599</v>
       </c>
       <c r="K4" t="n">
-        <v>6.937</v>
+        <v>26.6935</v>
       </c>
       <c r="L4" t="n">
-        <v>6.110300000000001</v>
+        <v>16.7661</v>
       </c>
       <c r="M4" t="n">
-        <v>-12.66</v>
+        <v>-32.108</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.4021</v>
+        <v>-11.7718</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.2583</v>
+        <v>-20.3362</v>
       </c>
       <c r="P4" t="n">
-        <v>17.0723</v>
+        <v>17.7552</v>
       </c>
       <c r="Q4" t="n">
-        <v>-10.9264</v>
+        <v>-34.6002</v>
       </c>
       <c r="R4" t="n">
-        <v>27.9988</v>
+        <v>52.3557</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.293</v>
+        <v>4.9067</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.9237</v>
+        <v>0.07110000000000005</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6305999999999998</v>
+        <v>4.8355</v>
       </c>
       <c r="V4" t="n">
-        <v>-8.930099999999999</v>
+        <v>-28.4594</v>
       </c>
       <c r="W4" t="n">
-        <v>1.822</v>
+        <v>13.2465</v>
       </c>
       <c r="X4" t="n">
-        <v>-10.7517</v>
+        <v>-41.7057</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>L. MANIEMA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>4.672199999999999</v>
+        <v>2.89</v>
       </c>
       <c r="E5" t="n">
-        <v>9.504899999999999</v>
+        <v>0.5287000000000002</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.8325</v>
+        <v>2.3612</v>
       </c>
       <c r="G5" t="n">
-        <v>3.849399999999999</v>
+        <v>-2.1853</v>
       </c>
       <c r="H5" t="n">
-        <v>6.693499999999999</v>
+        <v>-0.4776</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.8441</v>
+        <v>-1.708</v>
       </c>
       <c r="J5" t="n">
-        <v>22.0411</v>
+        <v>-0.8724999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>14.9367</v>
+        <v>1.1613</v>
       </c>
       <c r="L5" t="n">
-        <v>7.1044</v>
+        <v>-2.0338</v>
       </c>
       <c r="M5" t="n">
-        <v>-18.1914</v>
+        <v>-1.3128</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.2431</v>
+        <v>-1.6391</v>
       </c>
       <c r="O5" t="n">
-        <v>-9.948500000000001</v>
+        <v>0.3257</v>
       </c>
       <c r="P5" t="n">
-        <v>4.7804</v>
+        <v>4.7802</v>
       </c>
       <c r="Q5" t="n">
-        <v>-25.4947</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>30.275</v>
+        <v>6.146</v>
       </c>
       <c r="S5" t="n">
-        <v>14.918</v>
+        <v>0.8942000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>11.6516</v>
+        <v>0.8885</v>
       </c>
       <c r="U5" t="n">
-        <v>3.2661</v>
+        <v>0.005399999999999919</v>
       </c>
       <c r="V5" t="n">
-        <v>-18.8752</v>
+        <v>-0.5988</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3071</v>
+        <v>1.8785</v>
       </c>
       <c r="X5" t="n">
-        <v>-20.1821</v>
+        <v>-2.4771</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. MANIEMA</t>
+          <t>M. MITEO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3056</v>
+        <v>1.1811</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7618</v>
+        <v>1.9412</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5435</v>
+        <v>-0.76</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1853</v>
+        <v>1.3018</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4776</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.708</v>
+        <v>0.3711</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8724999999999999</v>
+        <v>1.4594</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1613</v>
+        <v>1.3476</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.0338</v>
+        <v>0.1117</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3128</v>
+        <v>-0.1576</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6391</v>
+        <v>-0.417</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3257</v>
+        <v>0.2593</v>
       </c>
       <c r="P6" t="n">
-        <v>4.7802</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3658</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>6.146</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3095</v>
+        <v>-0.6654</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1218</v>
+        <v>-0.1721</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8123</v>
+        <v>-0.4934</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5988</v>
+        <v>0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8785</v>
+        <v>1.792</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4771</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MITEO</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6166</v>
+        <v>-3.2441</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3453</v>
+        <v>1.4858</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7286999999999999</v>
+        <v>-4.729500000000002</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3018</v>
+        <v>3.849399999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9308999999999999</v>
+        <v>6.693499999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3711</v>
+        <v>-2.8441</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4594</v>
+        <v>22.0411</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3476</v>
+        <v>14.9367</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1117</v>
+        <v>7.1044</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1576</v>
+        <v>-18.1914</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.417</v>
+        <v>-8.2431</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2593</v>
+        <v>-9.948500000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>4.7804</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1382</v>
+        <v>-25.4947</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1382</v>
+        <v>30.275</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.23</v>
+        <v>7.001399999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.232</v>
+        <v>3.6322</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.462</v>
+        <v>3.369</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5447</v>
+        <v>-18.8752</v>
       </c>
       <c r="W7" t="n">
-        <v>1.792</v>
+        <v>1.3071</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2472</v>
+        <v>-20.1821</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0992</v>
+        <v>-3.8592</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5499999999999998</v>
+        <v>0.9759999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.549100000000001</v>
+        <v>-4.835199999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-6.093800000000001</v>
@@ -1078,13 +1078,13 @@
         <v>15.9341</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3023</v>
+        <v>2.5424</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4548</v>
+        <v>1.0713</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7568</v>
+        <v>1.4711</v>
       </c>
       <c r="V8" t="n">
         <v>-3.4948</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.950599999999998</v>
+        <v>-4.0785</v>
       </c>
       <c r="E9" t="n">
-        <v>15.8195</v>
+        <v>-7.2178</v>
       </c>
       <c r="F9" t="n">
-        <v>-20.7702</v>
+        <v>3.1387</v>
       </c>
       <c r="G9" t="n">
-        <v>-16.1531</v>
+        <v>-17.3955</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3528</v>
+        <v>-13.2882</v>
       </c>
       <c r="I9" t="n">
-        <v>-19.5056</v>
+        <v>-4.107200000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>18.4901</v>
+        <v>-5.980900000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>21.4416</v>
+        <v>-3.4128</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.9517</v>
+        <v>-2.5684</v>
       </c>
       <c r="M9" t="n">
-        <v>-34.6434</v>
+        <v>-11.4147</v>
       </c>
       <c r="N9" t="n">
-        <v>-18.0887</v>
+        <v>-9.8759</v>
       </c>
       <c r="O9" t="n">
-        <v>-16.5543</v>
+        <v>-1.5388</v>
       </c>
       <c r="P9" t="n">
-        <v>13.4304</v>
+        <v>13.2025</v>
       </c>
       <c r="Q9" t="n">
-        <v>-34.8279</v>
+        <v>-6.6014</v>
       </c>
       <c r="R9" t="n">
-        <v>48.2582</v>
+        <v>19.8039</v>
       </c>
       <c r="S9" t="n">
-        <v>25.9409</v>
+        <v>-0.006400000000000072</v>
       </c>
       <c r="T9" t="n">
-        <v>17.634</v>
+        <v>0.9918999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>8.307599999999999</v>
+        <v>-0.9983000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-28.1685</v>
+        <v>0.1202999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>14.5233</v>
+        <v>4.3729</v>
       </c>
       <c r="X9" t="n">
-        <v>-42.6917</v>
+        <v>-4.2526</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>B. JEFFERSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9811</v>
+        <v>-7.5843</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.9912</v>
+        <v>-5.286700000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0099</v>
+        <v>-2.2978</v>
       </c>
       <c r="G10" t="n">
-        <v>-17.3955</v>
+        <v>-2.2592</v>
       </c>
       <c r="H10" t="n">
-        <v>-13.2882</v>
+        <v>-5.0317</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.107200000000001</v>
+        <v>2.7727</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.980900000000001</v>
+        <v>1.1257</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.4128</v>
+        <v>-1.3661</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.5684</v>
+        <v>2.4915</v>
       </c>
       <c r="M10" t="n">
-        <v>-11.4147</v>
+        <v>-3.3847</v>
       </c>
       <c r="N10" t="n">
-        <v>-9.8759</v>
+        <v>-3.6657</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5388</v>
+        <v>0.281</v>
       </c>
       <c r="P10" t="n">
-        <v>13.2025</v>
+        <v>0.2277000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.6014</v>
+        <v>-4.7803</v>
       </c>
       <c r="R10" t="n">
-        <v>19.8039</v>
+        <v>5.008</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9087000000000003</v>
+        <v>-2.6714</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2184000000000002</v>
+        <v>-2.8793</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.127</v>
+        <v>0.208</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1202999999999999</v>
+        <v>-2.8814</v>
       </c>
       <c r="W10" t="n">
-        <v>4.3729</v>
+        <v>1.2473</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.2526</v>
+        <v>-4.1287</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. JEFFERSON</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.2139</v>
+        <v>-9.839900000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6593</v>
+        <v>-14.5654</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5545</v>
+        <v>4.724799999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2592</v>
+        <v>-2.496099999999998</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.0317</v>
+        <v>-4.1967</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7727</v>
+        <v>1.700199999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1257</v>
+        <v>6.9053</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3661</v>
+        <v>1.0451</v>
       </c>
       <c r="L11" t="n">
-        <v>2.4915</v>
+        <v>5.8602</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3847</v>
+        <v>-9.4017</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.6657</v>
+        <v>-5.241400000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.281</v>
+        <v>-4.1601</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2277000000000001</v>
+        <v>-5.4631</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.7803</v>
+        <v>-34.1452</v>
       </c>
       <c r="R11" t="n">
-        <v>5.008</v>
+        <v>28.6817</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.3009</v>
+        <v>2.5573</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.2518</v>
+        <v>3.7859</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0491</v>
+        <v>-1.2282</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.8814</v>
+        <v>-4.4383</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2473</v>
+        <v>8.888399999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.1287</v>
+        <v>-13.3267</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>C. ALOCEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.6647</v>
+        <v>-12.7892</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.6181</v>
+        <v>-15.7463</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9536</v>
+        <v>2.9576</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.496099999999998</v>
+        <v>-0.1107000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.1967</v>
+        <v>-1.039400000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>1.700199999999999</v>
+        <v>0.9280999999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>6.9053</v>
+        <v>10.1832</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0451</v>
+        <v>6.351100000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>5.8602</v>
+        <v>3.832</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.4017</v>
+        <v>-10.2942</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.241400000000001</v>
+        <v>-7.3902</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.1601</v>
+        <v>-2.904</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.4631</v>
+        <v>-17.3002</v>
       </c>
       <c r="Q12" t="n">
-        <v>-34.1452</v>
+        <v>-31.1857</v>
       </c>
       <c r="R12" t="n">
-        <v>28.6817</v>
+        <v>13.8857</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7331</v>
+        <v>-0.5962999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>6.7328</v>
+        <v>-2.9301</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.9996</v>
+        <v>2.3334</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.4383</v>
+        <v>5.2182</v>
       </c>
       <c r="W12" t="n">
-        <v>8.888399999999999</v>
+        <v>8.1861</v>
       </c>
       <c r="X12" t="n">
-        <v>-13.3267</v>
+        <v>-2.9678</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. ALOCEN</t>
+          <t>B. ANGOLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.2193</v>
+        <v>-16.8015</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.5786</v>
+        <v>-15.241</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3598</v>
+        <v>-1.5605</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1107000000000001</v>
+        <v>-12.0341</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.039400000000001</v>
+        <v>-8.3781</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9280999999999998</v>
+        <v>-3.656100000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>10.1832</v>
+        <v>-1.2879</v>
       </c>
       <c r="K13" t="n">
-        <v>6.351100000000001</v>
+        <v>-4.577</v>
       </c>
       <c r="L13" t="n">
-        <v>3.832</v>
+        <v>3.288900000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.2942</v>
+        <v>-10.746</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.3902</v>
+        <v>-3.8012</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.904</v>
+        <v>-6.944599999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-17.3002</v>
+        <v>-5.2355</v>
       </c>
       <c r="Q13" t="n">
-        <v>-31.1857</v>
+        <v>-26.8608</v>
       </c>
       <c r="R13" t="n">
-        <v>13.8857</v>
+        <v>21.6252</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.0263</v>
+        <v>-0.9368000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.762</v>
+        <v>0.8935000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7358</v>
+        <v>-1.8305</v>
       </c>
       <c r="V13" t="n">
-        <v>5.2182</v>
+        <v>1.405</v>
       </c>
       <c r="W13" t="n">
-        <v>8.1861</v>
+        <v>12.014</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.9678</v>
+        <v>-10.609</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.8845</v>
+        <v>-17.9291</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.5345</v>
+        <v>-15.3045</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3501</v>
+        <v>-2.6246</v>
       </c>
       <c r="G14" t="n">
         <v>-7.9374</v>
@@ -1546,13 +1546,13 @@
         <v>18.4381</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.2694</v>
+        <v>-3.3141</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.8622</v>
+        <v>-6.6322</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5926</v>
+        <v>3.3179</v>
       </c>
       <c r="V14" t="n">
         <v>8.3461</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. ANGOLA</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>-19.7123</v>
+        <v>-24.0504</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.391</v>
+        <v>-13.7869</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.321200000000001</v>
+        <v>-10.2639</v>
       </c>
       <c r="G15" t="n">
-        <v>-12.0341</v>
+        <v>-14.7218</v>
       </c>
       <c r="H15" t="n">
-        <v>-8.3781</v>
+        <v>-0.9595999999999993</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.656100000000001</v>
+        <v>-13.7623</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.2879</v>
+        <v>35.6272</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.577</v>
+        <v>27.4363</v>
       </c>
       <c r="L15" t="n">
-        <v>3.288900000000001</v>
+        <v>8.190999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-10.746</v>
+        <v>-50.3492</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.8012</v>
+        <v>-28.396</v>
       </c>
       <c r="O15" t="n">
-        <v>-6.944599999999999</v>
+        <v>-21.9533</v>
       </c>
       <c r="P15" t="n">
-        <v>-5.2355</v>
+        <v>0.9105999999999987</v>
       </c>
       <c r="Q15" t="n">
-        <v>-26.8608</v>
+        <v>-71.93170000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>21.6252</v>
+        <v>72.8421</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.8477</v>
+        <v>-10.2754</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2564999999999998</v>
+        <v>-11.7592</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.5913</v>
+        <v>1.484</v>
       </c>
       <c r="V15" t="n">
-        <v>1.405</v>
+        <v>0.0363</v>
       </c>
       <c r="W15" t="n">
-        <v>12.014</v>
+        <v>34.2768</v>
       </c>
       <c r="X15" t="n">
-        <v>-10.609</v>
+        <v>-34.2402</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>-37.524</v>
+        <v>-24.8755</v>
       </c>
       <c r="E16" t="n">
-        <v>-25.7014</v>
+        <v>-0.4767000000000008</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.8223</v>
+        <v>-24.3987</v>
       </c>
       <c r="G16" t="n">
-        <v>-14.7218</v>
+        <v>-16.1531</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9595999999999993</v>
+        <v>3.3528</v>
       </c>
       <c r="I16" t="n">
-        <v>-13.7623</v>
+        <v>-19.5056</v>
       </c>
       <c r="J16" t="n">
-        <v>35.6272</v>
+        <v>18.4901</v>
       </c>
       <c r="K16" t="n">
-        <v>27.4363</v>
+        <v>21.4416</v>
       </c>
       <c r="L16" t="n">
-        <v>8.190999999999999</v>
+        <v>-2.9517</v>
       </c>
       <c r="M16" t="n">
-        <v>-50.3492</v>
+        <v>-34.6434</v>
       </c>
       <c r="N16" t="n">
-        <v>-28.396</v>
+        <v>-18.0887</v>
       </c>
       <c r="O16" t="n">
-        <v>-21.9533</v>
+        <v>-16.5543</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9105999999999987</v>
+        <v>13.4304</v>
       </c>
       <c r="Q16" t="n">
-        <v>-71.93170000000001</v>
+        <v>-34.8279</v>
       </c>
       <c r="R16" t="n">
-        <v>72.8421</v>
+        <v>48.2582</v>
       </c>
       <c r="S16" t="n">
-        <v>-23.7487</v>
+        <v>6.0163</v>
       </c>
       <c r="T16" t="n">
-        <v>-23.6739</v>
+        <v>1.3374</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.07499999999999984</v>
+        <v>4.6788</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0363</v>
+        <v>-28.1685</v>
       </c>
       <c r="W16" t="n">
-        <v>34.2768</v>
+        <v>14.5233</v>
       </c>
       <c r="X16" t="n">
-        <v>-34.2402</v>
+        <v>-42.6917</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>-46.4258</v>
+        <v>-34.8169</v>
       </c>
       <c r="E17" t="n">
-        <v>-38.866</v>
+        <v>-30.8738</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.5597</v>
+        <v>-3.9429</v>
       </c>
       <c r="G17" t="n">
         <v>-24.9571</v>
@@ -1780,13 +1780,13 @@
         <v>26.6331</v>
       </c>
       <c r="S17" t="n">
-        <v>-20.3801</v>
+        <v>-8.7713</v>
       </c>
       <c r="T17" t="n">
-        <v>-15.1544</v>
+        <v>-7.1626</v>
       </c>
       <c r="U17" t="n">
-        <v>-5.2253</v>
+        <v>-1.6085</v>
       </c>
       <c r="V17" t="n">
         <v>5.0574</v>
@@ -1813,13 +1813,13 @@
         <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>-75.5706</v>
+        <v>-55.1422</v>
       </c>
       <c r="E18" t="n">
-        <v>-59.7932</v>
+        <v>-48.6592</v>
       </c>
       <c r="F18" t="n">
-        <v>-15.777</v>
+        <v>-6.482900000000001</v>
       </c>
       <c r="G18" t="n">
         <v>-35.8247</v>
@@ -1858,13 +1858,13 @@
         <v>55.9974</v>
       </c>
       <c r="S18" t="n">
-        <v>-32.775</v>
+        <v>-12.3465</v>
       </c>
       <c r="T18" t="n">
-        <v>-20.2425</v>
+        <v>-9.1081</v>
       </c>
       <c r="U18" t="n">
-        <v>-12.5325</v>
+        <v>-3.2382</v>
       </c>
       <c r="V18" t="n">
         <v>-2.645299999999999</v>
@@ -1891,13 +1891,13 @@
         <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>-181.7741</v>
+        <v>-153.1565</v>
       </c>
       <c r="E19" t="n">
-        <v>-103.9387</v>
+        <v>-93.48400000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-77.8339</v>
+        <v>-59.67290000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-111.9147</v>
@@ -1906,7 +1906,7 @@
         <v>-46.0346</v>
       </c>
       <c r="I19" t="n">
-        <v>-65.88079999999999</v>
+        <v>-65.88080000000001</v>
       </c>
       <c r="J19" t="n">
         <v>208.1189</v>
@@ -1915,7 +1915,7 @@
         <v>124.5312</v>
       </c>
       <c r="L19" t="n">
-        <v>83.58659999999999</v>
+        <v>83.5866</v>
       </c>
       <c r="M19" t="n">
         <v>-320.0336</v>
@@ -1936,13 +1936,13 @@
         <v>498.5146999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>-55.7523</v>
+        <v>-27.1355</v>
       </c>
       <c r="T19" t="n">
-        <v>-51.82259999999999</v>
+        <v>-41.3693</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.929100000000004</v>
+        <v>14.2327</v>
       </c>
       <c r="V19" t="n">
         <v>-36.8686</v>
